--- a/technology_surveys/046_software_api_release_developer_feedback_form--technology_surveys.xlsx
+++ b/technology_surveys/046_software_api_release_developer_feedback_form--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Category 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>title_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
